--- a/decisionmatrixproject/Lighthouse Decision Matrix.xlsx
+++ b/decisionmatrixproject/Lighthouse Decision Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John\Desktop\rhode\freeCodeCampEXCEL\Project3_DecisionMatrix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAB1ABBA-0DF8-4724-83A2-C7A1A4B66413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E46F76D7-1196-41D4-BACA-AA7B915E1F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="2670" windowWidth="33240" windowHeight="15885" xr2:uid="{6D1BAE02-1BD3-4172-B6AE-0B7BF42C3F5F}"/>
+    <workbookView xWindow="2985" yWindow="2205" windowWidth="33240" windowHeight="15885" xr2:uid="{6D1BAE02-1BD3-4172-B6AE-0B7BF42C3F5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Lighthouse Decision Matrix" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Lighthouse</t>
   </si>
@@ -85,12 +85,15 @@
   <si>
     <t xml:space="preserve">Total Formula </t>
   </si>
+  <si>
+    <t>MOST FINACIALY VIABLE PROJECT</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,6 +105,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -124,9 +135,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -142,6 +154,1222 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Lighthouse Preservation</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Priorities</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lighthouse Decision Matrix'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>West Point Lighthouse (Seattle)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lighthouse Decision Matrix'!$B$2:$K$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-861A-4902-9F2B-29A079B23600}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lighthouse Decision Matrix'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Admirality Head Lighthouse (Whidbey Island)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lighthouse Decision Matrix'!$B$3:$K$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.1000000000000014</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-861A-4902-9F2B-29A079B23600}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lighthouse Decision Matrix'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Lime Kiln Lighthouse (San Juan Island)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lighthouse Decision Matrix'!$B$4:$K$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11.699999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-861A-4902-9F2B-29A079B23600}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lighthouse Decision Matrix'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cape Disappointment Lighthouse (Long Beach Peninsual)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lighthouse Decision Matrix'!$B$5:$K$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4.5000000000000036</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-861A-4902-9F2B-29A079B23600}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Lighthouse Decision Matrix'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cape Flattery Light (remote, Olympic coast)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'Lighthouse Decision Matrix'!$B$6:$K$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-861A-4902-9F2B-29A079B23600}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1433551248"/>
+        <c:axId val="1433550288"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1433551248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1433550288"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1433550288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1433551248"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12274398169533038"/>
+          <c:y val="0.70922398511564866"/>
+          <c:w val="0.78651249415740843"/>
+          <c:h val="0.14131707664018475"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>981074</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1209674</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{697A0E19-D83A-AC18-44DF-C0F2A2FC3D01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,7 +1692,7 @@
   <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="53" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -473,7 +1701,8 @@
     <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="29" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -691,11 +1920,22 @@
         <v>-4.75</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="K9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="K10" t="str">
+        <f>INDEX(A3:A7,MATCH(MAX(K3:K7),K3:K7,0))</f>
+        <v>Lime Kiln Lighthouse (San Juan Island)</v>
+      </c>
+    </row>
     <row r="19" spans="11:11">
       <c r="K19" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K1:K1048576">
+  <conditionalFormatting sqref="K12:K1048576 K1:K10">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -718,5 +1958,6 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1899, NHL status" sqref="J3" xr:uid="{E20EF391-12B3-4874-A4E5-70F5929C5237}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>